--- a/ABA_mining/outputs/eval/task3/staff/llama3.2/zero_shot/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/staff/llama3.2/zero_shot/EVAL_SUMMARY.xlsx
@@ -541,13 +541,13 @@
         <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3768996960486322</v>
+        <v>0.3769</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8104575163398693</v>
+        <v>0.810458</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5145228215767635</v>
+        <v>0.514523</v>
       </c>
       <c r="O2" t="n">
         <v>0.532</v>
@@ -600,13 +600,13 @@
         <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3723723723723724</v>
+        <v>0.372372</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8104575163398693</v>
+        <v>0.810458</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5102880658436214</v>
+        <v>0.510288</v>
       </c>
       <c r="O3" t="n">
         <v>0.524</v>
@@ -659,13 +659,13 @@
         <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3716012084592145</v>
+        <v>0.371601</v>
       </c>
       <c r="M4" t="n">
-        <v>0.803921568627451</v>
+        <v>0.803922</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5082644628099173</v>
+        <v>0.508264</v>
       </c>
       <c r="O4" t="n">
         <v>0.524</v>
@@ -784,16 +784,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.3736153071500504</v>
+        <v>0.373615</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8082788671023965</v>
+        <v>0.808279</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5110192837465565</v>
+        <v>0.511019</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5266666666666666</v>
+        <v>0.526667</v>
       </c>
       <c r="J2" t="n">
         <v>1500</v>
